--- a/arquivos/ids_provedores_bl.xlsx
+++ b/arquivos/ids_provedores_bl.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\BLC TERCEIROS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\BLC TERCEIROS\arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0476FC03-873F-4FCB-8F76-73C809DF90D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7031E697-7595-47EA-9D67-79FB1F2BA6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$586</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$601</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2033" uniqueCount="797">
   <si>
     <t>TEIA</t>
   </si>
@@ -2117,52 +2117,319 @@
     <t>ACESSOLINE</t>
   </si>
   <si>
-    <t>GIGAMAIS - BL - CE</t>
-  </si>
-  <si>
-    <t>GIGAMAIS - BL - DF</t>
-  </si>
-  <si>
-    <t>GIGAMAIS - BL - ES</t>
-  </si>
-  <si>
-    <t>GIGAMAIS - BL - MA</t>
-  </si>
-  <si>
-    <t>GIGAMAIS - BL - MG</t>
-  </si>
-  <si>
-    <t>GIGAMAIS - BL - PA</t>
-  </si>
-  <si>
-    <t>GIGAMAIS - BL - PB</t>
-  </si>
-  <si>
-    <t>GIGAMAIS - BL - PE</t>
-  </si>
-  <si>
-    <t>GIGAMAIS - BL - PI</t>
-  </si>
-  <si>
-    <t>GIGAMAIS - BL - PR</t>
-  </si>
-  <si>
-    <t>GIGAMAIS - BL - RJ</t>
-  </si>
-  <si>
-    <t>GIGAMAIS - BL - RN</t>
-  </si>
-  <si>
-    <t>GIGAMAIS - BL - SE</t>
-  </si>
-  <si>
-    <t>GIGAMAIS - BL - SP</t>
-  </si>
-  <si>
-    <t>GIGAMAIS - BL - TO</t>
-  </si>
-  <si>
     <t>GIGA+</t>
+  </si>
+  <si>
+    <t>ATIVA TELECOM -BANDA LARGA- MG</t>
+  </si>
+  <si>
+    <t>BRASIL TECPAR -BANDA LARGA -MT</t>
+  </si>
+  <si>
+    <t>BRFIBRA</t>
+  </si>
+  <si>
+    <t>BRSULNET - BANDA LARGA - RS</t>
+  </si>
+  <si>
+    <t>CLICK IP - BANDA LARGA - AM</t>
+  </si>
+  <si>
+    <t>CLICK IP - BANDA LARGA - PA</t>
+  </si>
+  <si>
+    <t>ELO SOLUCOES - BANDA LARGA -GO</t>
+  </si>
+  <si>
+    <t>ELO SOLUCOES - BANDA LARGA -SP</t>
+  </si>
+  <si>
+    <t>GENERICO - BANDA LARGA</t>
+  </si>
+  <si>
+    <t>MAXBR TELECOM - BANDA LARGA - MG</t>
+  </si>
+  <si>
+    <t>S2BTI BANDA LARGA - MS</t>
+  </si>
+  <si>
+    <t>S2BTI BANDA LARGA - RO</t>
+  </si>
+  <si>
+    <t>S2BTI BANDA LARGA - RR</t>
+  </si>
+  <si>
+    <t>SARTOR - BANDA LARGA - MT</t>
+  </si>
+  <si>
+    <t>SCREEN SAVER - BANDA LARGA - BA</t>
+  </si>
+  <si>
+    <t>STAR1 - BANDA LARGA - MA</t>
+  </si>
+  <si>
+    <t>UNIFIQUE - BANDA LARGA - PR</t>
+  </si>
+  <si>
+    <t>WAVEMAX - BANDA LARGA - MT</t>
+  </si>
+  <si>
+    <t>WGO MULTIMÍDIA - BANDA LARGA - GO</t>
+  </si>
+  <si>
+    <t>[VIP+ TELECOM] - BANDA LARGA - RS</t>
+  </si>
+  <si>
+    <t>1TELECOM - BANDA LARGA - AL</t>
+  </si>
+  <si>
+    <t>1TELECOM - BANDA LARGA - BA</t>
+  </si>
+  <si>
+    <t>1TELECOM - BANDA LARGA - CE</t>
+  </si>
+  <si>
+    <t>1TELECOM - BANDA LARGA - PB</t>
+  </si>
+  <si>
+    <t>1TELECOM - BANDA LARGA - PE</t>
+  </si>
+  <si>
+    <t>1TELECOM - BANDA LARGA - SE</t>
+  </si>
+  <si>
+    <t>67 TELECOM - BANDA LARGA - MS</t>
+  </si>
+  <si>
+    <t>ACESSOLINE - BANDA LARGA - MG</t>
+  </si>
+  <si>
+    <t>ALARES - BANDA LARGA - AL</t>
+  </si>
+  <si>
+    <t>ALARES - BANDA LARGA - BA</t>
+  </si>
+  <si>
+    <t>ALARES - BANDA LARGA - CE</t>
+  </si>
+  <si>
+    <t>ALARES - BANDA LARGA - MG</t>
+  </si>
+  <si>
+    <t>ALARES - BANDA LARGA - PB</t>
+  </si>
+  <si>
+    <t>ALARES - BANDA LARGA - PR</t>
+  </si>
+  <si>
+    <t>ALARES - BANDA LARGA - SP</t>
+  </si>
+  <si>
+    <t>ALLREDE - BANDA LARGA - DF</t>
+  </si>
+  <si>
+    <t>ALLREDE - BANDA LARGA - GO</t>
+  </si>
+  <si>
+    <t>ALLREDE - BANDA LARGA - MG</t>
+  </si>
+  <si>
+    <t>ALLREDE - BANDA LARGA - MT</t>
+  </si>
+  <si>
+    <t>ARION - BANDA LARGA - AC</t>
+  </si>
+  <si>
+    <t>ARION - BANDA LARGA - AM</t>
+  </si>
+  <si>
+    <t>ARION - BANDA LARGA - RO</t>
+  </si>
+  <si>
+    <t>ARION - BANDA LARGA - RR</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - AL</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - BA</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - CE</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - DF</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - ES</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - GO</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - MA</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - MG</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - MS</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - MT</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - PB</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - PE</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - PI</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - PR</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - RJ</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - RN</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - RS</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - SC</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - SE</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - SP</t>
+  </si>
+  <si>
+    <t>BRFIBRA - BANDA LARGA - TO</t>
+  </si>
+  <si>
+    <t>IVI TELECOM BANDA LARGA - BA</t>
+  </si>
+  <si>
+    <t>LINQ TELECOM - BANDA LARGA - GO</t>
+  </si>
+  <si>
+    <t>ONLINE - BANDA LARGA - CE</t>
+  </si>
+  <si>
+    <t>ONLINE - BANDA LARGA - MA</t>
+  </si>
+  <si>
+    <t>ONLINE - BANDA LARGA - PA</t>
+  </si>
+  <si>
+    <t>ONLINE - BANDA LARGA - PI</t>
+  </si>
+  <si>
+    <t>SEBRATEL - BANDA LARGA - RS</t>
+  </si>
+  <si>
+    <t>SINAL BR - BANDA LARGA - SP</t>
+  </si>
+  <si>
+    <t>UFINET - BANDA LARGA - MG</t>
+  </si>
+  <si>
+    <t>UFINET - BANDA LARGA - RJ</t>
+  </si>
+  <si>
+    <t>UFINET - BANDA LARGA - SP</t>
+  </si>
+  <si>
+    <t>VERO - BANDA LARGA - ES</t>
+  </si>
+  <si>
+    <t>GIGAMAIS - BANDA LARGA - ES</t>
+  </si>
+  <si>
+    <t>1TELECOM</t>
+  </si>
+  <si>
+    <t>67 TELECOM</t>
+  </si>
+  <si>
+    <t>ALARES</t>
+  </si>
+  <si>
+    <t>ALL REDE</t>
+  </si>
+  <si>
+    <t>ARION</t>
+  </si>
+  <si>
+    <t>ATIVA TELECOM</t>
+  </si>
+  <si>
+    <t>BRASIL TECPAR</t>
+  </si>
+  <si>
+    <t>BRSULNET</t>
+  </si>
+  <si>
+    <t>CLICK IP</t>
+  </si>
+  <si>
+    <t>ELO SOLUCOES</t>
+  </si>
+  <si>
+    <t>GENERICO</t>
+  </si>
+  <si>
+    <t>IVI TELECOM</t>
+  </si>
+  <si>
+    <t>LINQ TELECOM</t>
+  </si>
+  <si>
+    <t>MAXBR TELECOM</t>
+  </si>
+  <si>
+    <t>ONLINE</t>
+  </si>
+  <si>
+    <t>S2BTI</t>
+  </si>
+  <si>
+    <t>SARTOR</t>
+  </si>
+  <si>
+    <t>SCREEN SAVER</t>
+  </si>
+  <si>
+    <t>SEBRATEL</t>
+  </si>
+  <si>
+    <t>SINAL BR</t>
+  </si>
+  <si>
+    <t>STAR1</t>
+  </si>
+  <si>
+    <t>UFINET</t>
+  </si>
+  <si>
+    <t>UNIFIQUE</t>
+  </si>
+  <si>
+    <t>VERO</t>
+  </si>
+  <si>
+    <t>WAVEMAX</t>
+  </si>
+  <si>
+    <t>WGO MULTIMIDIA</t>
+  </si>
+  <si>
+    <t>VIP+ TELECOM</t>
   </si>
 </sst>
 </file>
@@ -2481,7 +2748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D214076-1032-40E4-B727-75DC9C5ACC79}">
-  <dimension ref="A1:I601"/>
+  <dimension ref="A1:I677"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -12460,13 +12727,13 @@
         <v>1208</v>
       </c>
       <c r="B587" t="s">
-        <v>692</v>
+        <v>470</v>
       </c>
       <c r="C587">
         <v>1208</v>
       </c>
       <c r="D587" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="E587" t="s">
         <v>363</v>
@@ -12480,13 +12747,13 @@
         <v>1402</v>
       </c>
       <c r="B588" t="s">
-        <v>693</v>
+        <v>471</v>
       </c>
       <c r="C588">
         <v>1402</v>
       </c>
       <c r="D588" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="E588" t="s">
         <v>364</v>
@@ -12500,13 +12767,13 @@
         <v>1483</v>
       </c>
       <c r="B589" t="s">
-        <v>694</v>
+        <v>769</v>
       </c>
       <c r="C589">
         <v>1483</v>
       </c>
       <c r="D589" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="E589" t="s">
         <v>365</v>
@@ -12520,13 +12787,13 @@
         <v>1209</v>
       </c>
       <c r="B590" t="s">
-        <v>695</v>
+        <v>472</v>
       </c>
       <c r="C590">
         <v>1209</v>
       </c>
       <c r="D590" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="E590" t="s">
         <v>367</v>
@@ -12540,13 +12807,13 @@
         <v>1382</v>
       </c>
       <c r="B591" t="s">
-        <v>696</v>
+        <v>473</v>
       </c>
       <c r="C591">
         <v>1382</v>
       </c>
       <c r="D591" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="E591" t="s">
         <v>368</v>
@@ -12560,13 +12827,13 @@
         <v>1403</v>
       </c>
       <c r="B592" t="s">
-        <v>697</v>
+        <v>474</v>
       </c>
       <c r="C592">
         <v>1403</v>
       </c>
       <c r="D592" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="E592" t="s">
         <v>371</v>
@@ -12580,13 +12847,13 @@
         <v>1210</v>
       </c>
       <c r="B593" t="s">
-        <v>698</v>
+        <v>475</v>
       </c>
       <c r="C593">
         <v>1210</v>
       </c>
       <c r="D593" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="E593" t="s">
         <v>372</v>
@@ -12600,13 +12867,13 @@
         <v>1211</v>
       </c>
       <c r="B594" t="s">
-        <v>699</v>
+        <v>476</v>
       </c>
       <c r="C594">
         <v>1211</v>
       </c>
       <c r="D594" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="E594" t="s">
         <v>373</v>
@@ -12620,13 +12887,13 @@
         <v>1212</v>
       </c>
       <c r="B595" t="s">
-        <v>700</v>
+        <v>477</v>
       </c>
       <c r="C595">
         <v>1212</v>
       </c>
       <c r="D595" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="E595" t="s">
         <v>374</v>
@@ -12640,13 +12907,13 @@
         <v>1213</v>
       </c>
       <c r="B596" t="s">
-        <v>701</v>
+        <v>478</v>
       </c>
       <c r="C596">
         <v>1213</v>
       </c>
       <c r="D596" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="E596" t="s">
         <v>358</v>
@@ -12660,13 +12927,13 @@
         <v>1214</v>
       </c>
       <c r="B597" t="s">
-        <v>702</v>
+        <v>479</v>
       </c>
       <c r="C597">
         <v>1214</v>
       </c>
       <c r="D597" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="E597" t="s">
         <v>375</v>
@@ -12680,13 +12947,13 @@
         <v>1404</v>
       </c>
       <c r="B598" t="s">
-        <v>703</v>
+        <v>480</v>
       </c>
       <c r="C598">
         <v>1404</v>
       </c>
       <c r="D598" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="E598" t="s">
         <v>376</v>
@@ -12700,13 +12967,13 @@
         <v>1215</v>
       </c>
       <c r="B599" t="s">
-        <v>704</v>
+        <v>481</v>
       </c>
       <c r="C599">
         <v>1215</v>
       </c>
       <c r="D599" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="E599" t="s">
         <v>357</v>
@@ -12720,13 +12987,13 @@
         <v>1216</v>
       </c>
       <c r="B600" t="s">
-        <v>705</v>
+        <v>482</v>
       </c>
       <c r="C600">
         <v>1216</v>
       </c>
       <c r="D600" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="E600" t="s">
         <v>359</v>
@@ -12740,13 +13007,13 @@
         <v>1405</v>
       </c>
       <c r="B601" t="s">
-        <v>706</v>
+        <v>483</v>
       </c>
       <c r="C601">
         <v>1405</v>
       </c>
       <c r="D601" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="E601" t="s">
         <v>381</v>
@@ -12755,7 +13022,1300 @@
       <c r="H601" s="1"/>
       <c r="I601" s="1"/>
     </row>
+    <row r="602" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A602">
+        <v>1705</v>
+      </c>
+      <c r="B602" t="s">
+        <v>713</v>
+      </c>
+      <c r="C602">
+        <v>2917</v>
+      </c>
+      <c r="D602" t="s">
+        <v>770</v>
+      </c>
+      <c r="E602" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="603" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A603">
+        <v>1706</v>
+      </c>
+      <c r="B603" t="s">
+        <v>714</v>
+      </c>
+      <c r="C603">
+        <v>2918</v>
+      </c>
+      <c r="D603" t="s">
+        <v>770</v>
+      </c>
+      <c r="E603" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="604" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A604">
+        <v>1707</v>
+      </c>
+      <c r="B604" t="s">
+        <v>715</v>
+      </c>
+      <c r="C604">
+        <v>2919</v>
+      </c>
+      <c r="D604" t="s">
+        <v>770</v>
+      </c>
+      <c r="E604" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="605" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A605">
+        <v>1708</v>
+      </c>
+      <c r="B605" t="s">
+        <v>716</v>
+      </c>
+      <c r="C605">
+        <v>2920</v>
+      </c>
+      <c r="D605" t="s">
+        <v>770</v>
+      </c>
+      <c r="E605" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="606" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A606">
+        <v>1709</v>
+      </c>
+      <c r="B606" t="s">
+        <v>717</v>
+      </c>
+      <c r="C606">
+        <v>2921</v>
+      </c>
+      <c r="D606" t="s">
+        <v>770</v>
+      </c>
+      <c r="E606" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="607" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A607">
+        <v>1710</v>
+      </c>
+      <c r="B607" t="s">
+        <v>718</v>
+      </c>
+      <c r="C607">
+        <v>2922</v>
+      </c>
+      <c r="D607" t="s">
+        <v>770</v>
+      </c>
+      <c r="E607" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="608" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A608">
+        <v>1861</v>
+      </c>
+      <c r="B608" t="s">
+        <v>719</v>
+      </c>
+      <c r="C608">
+        <v>3036</v>
+      </c>
+      <c r="D608" t="s">
+        <v>771</v>
+      </c>
+      <c r="E608" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="609" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A609">
+        <v>1699</v>
+      </c>
+      <c r="B609" t="s">
+        <v>720</v>
+      </c>
+      <c r="C609">
+        <v>2916</v>
+      </c>
+      <c r="D609" t="s">
+        <v>691</v>
+      </c>
+      <c r="E609" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="610" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A610">
+        <v>1461</v>
+      </c>
+      <c r="B610" t="s">
+        <v>721</v>
+      </c>
+      <c r="C610">
+        <v>2703</v>
+      </c>
+      <c r="D610" t="s">
+        <v>772</v>
+      </c>
+      <c r="E610" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="611" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A611">
+        <v>1462</v>
+      </c>
+      <c r="B611" t="s">
+        <v>722</v>
+      </c>
+      <c r="C611">
+        <v>2698</v>
+      </c>
+      <c r="D611" t="s">
+        <v>772</v>
+      </c>
+      <c r="E611" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="612" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A612">
+        <v>1463</v>
+      </c>
+      <c r="B612" t="s">
+        <v>723</v>
+      </c>
+      <c r="C612">
+        <v>2700</v>
+      </c>
+      <c r="D612" t="s">
+        <v>772</v>
+      </c>
+      <c r="E612" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="613" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A613">
+        <v>1464</v>
+      </c>
+      <c r="B613" t="s">
+        <v>724</v>
+      </c>
+      <c r="C613">
+        <v>2699</v>
+      </c>
+      <c r="D613" t="s">
+        <v>772</v>
+      </c>
+      <c r="E613" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="614" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A614">
+        <v>1465</v>
+      </c>
+      <c r="B614" t="s">
+        <v>725</v>
+      </c>
+      <c r="C614">
+        <v>2701</v>
+      </c>
+      <c r="D614" t="s">
+        <v>772</v>
+      </c>
+      <c r="E614" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="615" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A615">
+        <v>1466</v>
+      </c>
+      <c r="B615" t="s">
+        <v>726</v>
+      </c>
+      <c r="C615">
+        <v>2702</v>
+      </c>
+      <c r="D615" t="s">
+        <v>772</v>
+      </c>
+      <c r="E615" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="616" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A616">
+        <v>1467</v>
+      </c>
+      <c r="B616" t="s">
+        <v>727</v>
+      </c>
+      <c r="C616">
+        <v>2704</v>
+      </c>
+      <c r="D616" t="s">
+        <v>772</v>
+      </c>
+      <c r="E616" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="617" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A617">
+        <v>1871</v>
+      </c>
+      <c r="B617" t="s">
+        <v>728</v>
+      </c>
+      <c r="C617">
+        <v>3126</v>
+      </c>
+      <c r="D617" t="s">
+        <v>773</v>
+      </c>
+      <c r="E617" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="618" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A618">
+        <v>1872</v>
+      </c>
+      <c r="B618" t="s">
+        <v>729</v>
+      </c>
+      <c r="C618">
+        <v>3127</v>
+      </c>
+      <c r="D618" t="s">
+        <v>773</v>
+      </c>
+      <c r="E618" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="619" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A619">
+        <v>1873</v>
+      </c>
+      <c r="B619" t="s">
+        <v>730</v>
+      </c>
+      <c r="C619">
+        <v>3125</v>
+      </c>
+      <c r="D619" t="s">
+        <v>773</v>
+      </c>
+      <c r="E619" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="620" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A620">
+        <v>1874</v>
+      </c>
+      <c r="B620" t="s">
+        <v>731</v>
+      </c>
+      <c r="C620">
+        <v>3128</v>
+      </c>
+      <c r="D620" t="s">
+        <v>773</v>
+      </c>
+      <c r="E620" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="621" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A621">
+        <v>1839</v>
+      </c>
+      <c r="B621" t="s">
+        <v>732</v>
+      </c>
+      <c r="C621">
+        <v>3094</v>
+      </c>
+      <c r="D621" t="s">
+        <v>774</v>
+      </c>
+      <c r="E621" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="622" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A622">
+        <v>1840</v>
+      </c>
+      <c r="B622" t="s">
+        <v>733</v>
+      </c>
+      <c r="C622">
+        <v>3095</v>
+      </c>
+      <c r="D622" t="s">
+        <v>774</v>
+      </c>
+      <c r="E622" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="623" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A623">
+        <v>1841</v>
+      </c>
+      <c r="B623" t="s">
+        <v>734</v>
+      </c>
+      <c r="C623">
+        <v>3096</v>
+      </c>
+      <c r="D623" t="s">
+        <v>774</v>
+      </c>
+      <c r="E623" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="624" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A624">
+        <v>1842</v>
+      </c>
+      <c r="B624" t="s">
+        <v>735</v>
+      </c>
+      <c r="C624">
+        <v>3097</v>
+      </c>
+      <c r="D624" t="s">
+        <v>774</v>
+      </c>
+      <c r="E624" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="625" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A625">
+        <v>1715</v>
+      </c>
+      <c r="B625" t="s">
+        <v>693</v>
+      </c>
+      <c r="C625">
+        <v>2925</v>
+      </c>
+      <c r="D625" t="s">
+        <v>775</v>
+      </c>
+      <c r="E625" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="626" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A626">
+        <v>1880</v>
+      </c>
+      <c r="B626" t="s">
+        <v>694</v>
+      </c>
+      <c r="C626">
+        <v>3054</v>
+      </c>
+      <c r="D626" t="s">
+        <v>776</v>
+      </c>
+      <c r="E626" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="627" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A627">
+        <v>1641</v>
+      </c>
+      <c r="B627" t="s">
+        <v>736</v>
+      </c>
+      <c r="C627">
+        <v>2873</v>
+      </c>
+      <c r="D627" t="s">
+        <v>695</v>
+      </c>
+      <c r="E627" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="628" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A628">
+        <v>1642</v>
+      </c>
+      <c r="B628" t="s">
+        <v>737</v>
+      </c>
+      <c r="C628">
+        <v>2874</v>
+      </c>
+      <c r="D628" t="s">
+        <v>695</v>
+      </c>
+      <c r="E628" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="629" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A629">
+        <v>1643</v>
+      </c>
+      <c r="B629" t="s">
+        <v>738</v>
+      </c>
+      <c r="C629">
+        <v>2875</v>
+      </c>
+      <c r="D629" t="s">
+        <v>695</v>
+      </c>
+      <c r="E629" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="630" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A630">
+        <v>1644</v>
+      </c>
+      <c r="B630" t="s">
+        <v>739</v>
+      </c>
+      <c r="C630">
+        <v>2876</v>
+      </c>
+      <c r="D630" t="s">
+        <v>695</v>
+      </c>
+      <c r="E630" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="631" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A631">
+        <v>1645</v>
+      </c>
+      <c r="B631" t="s">
+        <v>740</v>
+      </c>
+      <c r="C631">
+        <v>2877</v>
+      </c>
+      <c r="D631" t="s">
+        <v>695</v>
+      </c>
+      <c r="E631" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="632" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A632">
+        <v>1646</v>
+      </c>
+      <c r="B632" t="s">
+        <v>741</v>
+      </c>
+      <c r="C632">
+        <v>2878</v>
+      </c>
+      <c r="D632" t="s">
+        <v>695</v>
+      </c>
+      <c r="E632" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="633" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A633">
+        <v>1647</v>
+      </c>
+      <c r="B633" t="s">
+        <v>742</v>
+      </c>
+      <c r="C633">
+        <v>2879</v>
+      </c>
+      <c r="D633" t="s">
+        <v>695</v>
+      </c>
+      <c r="E633" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="634" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A634">
+        <v>1648</v>
+      </c>
+      <c r="B634" t="s">
+        <v>743</v>
+      </c>
+      <c r="C634">
+        <v>2880</v>
+      </c>
+      <c r="D634" t="s">
+        <v>695</v>
+      </c>
+      <c r="E634" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="635" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A635">
+        <v>1649</v>
+      </c>
+      <c r="B635" t="s">
+        <v>744</v>
+      </c>
+      <c r="C635">
+        <v>2881</v>
+      </c>
+      <c r="D635" t="s">
+        <v>695</v>
+      </c>
+      <c r="E635" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="636" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A636">
+        <v>1650</v>
+      </c>
+      <c r="B636" t="s">
+        <v>745</v>
+      </c>
+      <c r="C636">
+        <v>2882</v>
+      </c>
+      <c r="D636" t="s">
+        <v>695</v>
+      </c>
+      <c r="E636" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="637" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A637">
+        <v>1651</v>
+      </c>
+      <c r="B637" t="s">
+        <v>746</v>
+      </c>
+      <c r="C637">
+        <v>2883</v>
+      </c>
+      <c r="D637" t="s">
+        <v>695</v>
+      </c>
+      <c r="E637" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="638" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A638">
+        <v>1652</v>
+      </c>
+      <c r="B638" t="s">
+        <v>747</v>
+      </c>
+      <c r="C638">
+        <v>2885</v>
+      </c>
+      <c r="D638" t="s">
+        <v>695</v>
+      </c>
+      <c r="E638" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="639" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A639">
+        <v>1653</v>
+      </c>
+      <c r="B639" t="s">
+        <v>748</v>
+      </c>
+      <c r="C639">
+        <v>2886</v>
+      </c>
+      <c r="D639" t="s">
+        <v>695</v>
+      </c>
+      <c r="E639" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="640" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A640">
+        <v>1654</v>
+      </c>
+      <c r="B640" t="s">
+        <v>749</v>
+      </c>
+      <c r="C640">
+        <v>2887</v>
+      </c>
+      <c r="D640" t="s">
+        <v>695</v>
+      </c>
+      <c r="E640" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="641" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A641">
+        <v>1655</v>
+      </c>
+      <c r="B641" t="s">
+        <v>750</v>
+      </c>
+      <c r="C641">
+        <v>2888</v>
+      </c>
+      <c r="D641" t="s">
+        <v>695</v>
+      </c>
+      <c r="E641" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="642" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A642">
+        <v>1656</v>
+      </c>
+      <c r="B642" t="s">
+        <v>751</v>
+      </c>
+      <c r="C642">
+        <v>2889</v>
+      </c>
+      <c r="D642" t="s">
+        <v>695</v>
+      </c>
+      <c r="E642" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="643" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A643">
+        <v>1657</v>
+      </c>
+      <c r="B643" t="s">
+        <v>752</v>
+      </c>
+      <c r="C643">
+        <v>2890</v>
+      </c>
+      <c r="D643" t="s">
+        <v>695</v>
+      </c>
+      <c r="E643" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="644" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A644">
+        <v>1658</v>
+      </c>
+      <c r="B644" t="s">
+        <v>753</v>
+      </c>
+      <c r="C644">
+        <v>2891</v>
+      </c>
+      <c r="D644" t="s">
+        <v>695</v>
+      </c>
+      <c r="E644" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="645" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A645">
+        <v>1659</v>
+      </c>
+      <c r="B645" t="s">
+        <v>754</v>
+      </c>
+      <c r="C645">
+        <v>2892</v>
+      </c>
+      <c r="D645" t="s">
+        <v>695</v>
+      </c>
+      <c r="E645" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="646" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A646">
+        <v>1660</v>
+      </c>
+      <c r="B646" t="s">
+        <v>755</v>
+      </c>
+      <c r="C646">
+        <v>2893</v>
+      </c>
+      <c r="D646" t="s">
+        <v>695</v>
+      </c>
+      <c r="E646" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="647" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A647">
+        <v>1661</v>
+      </c>
+      <c r="B647" t="s">
+        <v>756</v>
+      </c>
+      <c r="C647">
+        <v>2894</v>
+      </c>
+      <c r="D647" t="s">
+        <v>695</v>
+      </c>
+      <c r="E647" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="648" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A648">
+        <v>1828</v>
+      </c>
+      <c r="B648" t="s">
+        <v>696</v>
+      </c>
+      <c r="C648">
+        <v>3044</v>
+      </c>
+      <c r="D648" t="s">
+        <v>777</v>
+      </c>
+      <c r="E648" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="649" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A649">
+        <v>1725</v>
+      </c>
+      <c r="B649" t="s">
+        <v>697</v>
+      </c>
+      <c r="C649">
+        <v>2931</v>
+      </c>
+      <c r="D649" t="s">
+        <v>778</v>
+      </c>
+      <c r="E649" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="650" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A650">
+        <v>1726</v>
+      </c>
+      <c r="B650" t="s">
+        <v>698</v>
+      </c>
+      <c r="C650">
+        <v>2932</v>
+      </c>
+      <c r="D650" t="s">
+        <v>778</v>
+      </c>
+      <c r="E650" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="651" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A651">
+        <v>1779</v>
+      </c>
+      <c r="B651" t="s">
+        <v>699</v>
+      </c>
+      <c r="C651">
+        <v>2987</v>
+      </c>
+      <c r="D651" t="s">
+        <v>779</v>
+      </c>
+      <c r="E651" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="652" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A652">
+        <v>1780</v>
+      </c>
+      <c r="B652" t="s">
+        <v>700</v>
+      </c>
+      <c r="C652">
+        <v>2988</v>
+      </c>
+      <c r="D652" t="s">
+        <v>779</v>
+      </c>
+      <c r="E652" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="653" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A653">
+        <v>1826</v>
+      </c>
+      <c r="B653" t="s">
+        <v>701</v>
+      </c>
+      <c r="C653">
+        <v>3041</v>
+      </c>
+      <c r="D653" t="s">
+        <v>780</v>
+      </c>
+      <c r="E653" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="654" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A654">
+        <v>1519</v>
+      </c>
+      <c r="B654" t="s">
+        <v>757</v>
+      </c>
+      <c r="C654">
+        <v>2713</v>
+      </c>
+      <c r="D654" t="s">
+        <v>781</v>
+      </c>
+      <c r="E654" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="655" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A655">
+        <v>1520</v>
+      </c>
+      <c r="B655" t="s">
+        <v>758</v>
+      </c>
+      <c r="C655">
+        <v>2688</v>
+      </c>
+      <c r="D655" t="s">
+        <v>782</v>
+      </c>
+      <c r="E655" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="656" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A656">
+        <v>1994</v>
+      </c>
+      <c r="B656" t="s">
+        <v>702</v>
+      </c>
+      <c r="C656">
+        <v>3238</v>
+      </c>
+      <c r="D656" t="s">
+        <v>783</v>
+      </c>
+      <c r="E656" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="657" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A657">
+        <v>1790</v>
+      </c>
+      <c r="B657" t="s">
+        <v>759</v>
+      </c>
+      <c r="C657">
+        <v>2991</v>
+      </c>
+      <c r="D657" t="s">
+        <v>784</v>
+      </c>
+      <c r="E657" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="658" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A658">
+        <v>1791</v>
+      </c>
+      <c r="B658" t="s">
+        <v>760</v>
+      </c>
+      <c r="C658">
+        <v>2992</v>
+      </c>
+      <c r="D658" t="s">
+        <v>784</v>
+      </c>
+      <c r="E658" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="659" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A659">
+        <v>1792</v>
+      </c>
+      <c r="B659" t="s">
+        <v>761</v>
+      </c>
+      <c r="C659">
+        <v>2993</v>
+      </c>
+      <c r="D659" t="s">
+        <v>784</v>
+      </c>
+      <c r="E659" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="660" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A660">
+        <v>1793</v>
+      </c>
+      <c r="B660" t="s">
+        <v>762</v>
+      </c>
+      <c r="C660">
+        <v>2994</v>
+      </c>
+      <c r="D660" t="s">
+        <v>784</v>
+      </c>
+      <c r="E660" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="661" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A661">
+        <v>1988</v>
+      </c>
+      <c r="B661" t="s">
+        <v>703</v>
+      </c>
+      <c r="C661">
+        <v>3224</v>
+      </c>
+      <c r="D661" t="s">
+        <v>785</v>
+      </c>
+      <c r="E661" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="662" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A662">
+        <v>1989</v>
+      </c>
+      <c r="B662" t="s">
+        <v>704</v>
+      </c>
+      <c r="C662">
+        <v>3223</v>
+      </c>
+      <c r="D662" t="s">
+        <v>785</v>
+      </c>
+      <c r="E662" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="663" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A663">
+        <v>1984</v>
+      </c>
+      <c r="B663" t="s">
+        <v>705</v>
+      </c>
+      <c r="C663">
+        <v>3222</v>
+      </c>
+      <c r="D663" t="s">
+        <v>785</v>
+      </c>
+      <c r="E663" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="664" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A664">
+        <v>1533</v>
+      </c>
+      <c r="B664" t="s">
+        <v>706</v>
+      </c>
+      <c r="C664">
+        <v>2693</v>
+      </c>
+      <c r="D664" t="s">
+        <v>786</v>
+      </c>
+      <c r="E664" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="665" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A665">
+        <v>1837</v>
+      </c>
+      <c r="B665" t="s">
+        <v>707</v>
+      </c>
+      <c r="C665">
+        <v>3053</v>
+      </c>
+      <c r="D665" t="s">
+        <v>787</v>
+      </c>
+      <c r="E665" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="666" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A666">
+        <v>1990</v>
+      </c>
+      <c r="B666" t="s">
+        <v>763</v>
+      </c>
+      <c r="C666">
+        <v>3230</v>
+      </c>
+      <c r="D666" t="s">
+        <v>788</v>
+      </c>
+      <c r="E666" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="667" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A667">
+        <v>1536</v>
+      </c>
+      <c r="B667" t="s">
+        <v>764</v>
+      </c>
+      <c r="C667">
+        <v>2667</v>
+      </c>
+      <c r="D667" t="s">
+        <v>789</v>
+      </c>
+      <c r="E667" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="668" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A668">
+        <v>1539</v>
+      </c>
+      <c r="B668" t="s">
+        <v>708</v>
+      </c>
+      <c r="C668">
+        <v>2686</v>
+      </c>
+      <c r="D668" t="s">
+        <v>790</v>
+      </c>
+      <c r="E668" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="669" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A669">
+        <v>1980</v>
+      </c>
+      <c r="B669" t="s">
+        <v>765</v>
+      </c>
+      <c r="C669">
+        <v>3167</v>
+      </c>
+      <c r="D669" t="s">
+        <v>791</v>
+      </c>
+      <c r="E669" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="670" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A670">
+        <v>1981</v>
+      </c>
+      <c r="B670" t="s">
+        <v>766</v>
+      </c>
+      <c r="C670">
+        <v>3165</v>
+      </c>
+      <c r="D670" t="s">
+        <v>791</v>
+      </c>
+      <c r="E670" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="671" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A671">
+        <v>1982</v>
+      </c>
+      <c r="B671" t="s">
+        <v>767</v>
+      </c>
+      <c r="C671">
+        <v>3166</v>
+      </c>
+      <c r="D671" t="s">
+        <v>791</v>
+      </c>
+      <c r="E671" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="672" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A672">
+        <v>1831</v>
+      </c>
+      <c r="B672" t="s">
+        <v>709</v>
+      </c>
+      <c r="C672">
+        <v>3076</v>
+      </c>
+      <c r="D672" t="s">
+        <v>792</v>
+      </c>
+      <c r="E672" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="673" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A673">
+        <v>1936</v>
+      </c>
+      <c r="B673" t="s">
+        <v>709</v>
+      </c>
+      <c r="C673">
+        <v>3075</v>
+      </c>
+      <c r="D673" t="s">
+        <v>792</v>
+      </c>
+      <c r="E673" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="674" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A674">
+        <v>1822</v>
+      </c>
+      <c r="B674" t="s">
+        <v>768</v>
+      </c>
+      <c r="C674">
+        <v>3005</v>
+      </c>
+      <c r="D674" t="s">
+        <v>793</v>
+      </c>
+      <c r="E674" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="675" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A675">
+        <v>1636</v>
+      </c>
+      <c r="B675" t="s">
+        <v>710</v>
+      </c>
+      <c r="C675">
+        <v>2714</v>
+      </c>
+      <c r="D675" t="s">
+        <v>794</v>
+      </c>
+      <c r="E675" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="676" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A676">
+        <v>1995</v>
+      </c>
+      <c r="B676" t="s">
+        <v>711</v>
+      </c>
+      <c r="C676">
+        <v>3240</v>
+      </c>
+      <c r="D676" t="s">
+        <v>795</v>
+      </c>
+      <c r="E676" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="677" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A677">
+        <v>1992</v>
+      </c>
+      <c r="B677" t="s">
+        <v>712</v>
+      </c>
+      <c r="C677">
+        <v>3236</v>
+      </c>
+      <c r="D677" t="s">
+        <v>796</v>
+      </c>
+      <c r="E677" t="s">
+        <v>379</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E601" xr:uid="{7D214076-1032-40E4-B727-75DC9C5ACC79}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
